--- a/docs/plantillas/pruebas/12-ERR-sin-depositos.xlsx
+++ b/docs/plantillas/pruebas/12-ERR-sin-depositos.xlsx
@@ -2679,7 +2679,7 @@
       </c>
       <c r="J2" s="51" t="inlineStr">
         <is>
-          <t>0012024001</t>
+          <t>00120240014</t>
         </is>
       </c>
     </row>
